--- a/table.xlsx
+++ b/table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raeltonhonorio/Documents/KDAM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5592E3C6-044A-CA44-888B-43DC96468160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0CF91C-73E6-DF49-B9DF-70E35B2B4795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{5B9D78BB-BF26-744A-AD4E-5FA2C52ED94A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{5B9D78BB-BF26-744A-AD4E-5FA2C52ED94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="161">
   <si>
     <t>setup</t>
   </si>
@@ -62,12 +62,6 @@
     <t>RGB Color Space Profile</t>
   </si>
   <si>
-    <t>Black  / STD</t>
-  </si>
-  <si>
-    <t>Black / High Production</t>
-  </si>
-  <si>
     <t>Atlas MAX+ Black HP</t>
   </si>
   <si>
@@ -83,26 +77,455 @@
     <t>Atlas MAX+ Light High Production</t>
   </si>
   <si>
-    <t>Light / High Production</t>
-  </si>
-  <si>
     <t>Atlas MAX+ Light High Production SatRGK</t>
   </si>
   <si>
     <t>Atlas MAX+ Black HQ</t>
   </si>
   <si>
-    <t>Black / HQ</t>
-  </si>
-  <si>
     <t>Atlas MAX+ Black HQ SatRGK</t>
+  </si>
+  <si>
+    <t>VULCAN SETUPS</t>
+  </si>
+  <si>
+    <t>AC Dark delay</t>
+  </si>
+  <si>
+    <t>AC Dark</t>
+  </si>
+  <si>
+    <t>AC NO WHITE UNDER BASE</t>
+  </si>
+  <si>
+    <t>Ac no white under</t>
+  </si>
+  <si>
+    <t>AC WHITE INK</t>
+  </si>
+  <si>
+    <t>Black Heather</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Calibration_1.kst</t>
+  </si>
+  <si>
+    <t>Calibration.kst</t>
+  </si>
+  <si>
+    <t>Color Stability.kst</t>
+  </si>
+  <si>
+    <t>D5S.kst</t>
+  </si>
+  <si>
+    <t>Dark 4C Highest Q V900.kst</t>
+  </si>
+  <si>
+    <t>Dark 4C HP V900.kst</t>
+  </si>
+  <si>
+    <t>Dark 4C HQ V900.kst</t>
+  </si>
+  <si>
+    <t>Dark 4C STD V900.kst</t>
+  </si>
+  <si>
+    <t>Dark Highest Q V900.kst</t>
+  </si>
+  <si>
+    <t>Dark HP 4C EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Dark HP 4C EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Dark HP EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Dark HP EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Dark HP V900.kst</t>
+  </si>
+  <si>
+    <t>Dark HQ 4C EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Dark HQ 4C EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Dark HQ EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Dark HQ EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Dark HQ V900.kst</t>
+  </si>
+  <si>
+    <t>Dark Standard.kst</t>
+  </si>
+  <si>
+    <t>Dark STD 4C EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Dark STD 4C EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Dark STD EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Dark STD EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Dark STD V900.kst</t>
+  </si>
+  <si>
+    <t>Darks.kst</t>
+  </si>
+  <si>
+    <t>Graphite.kst</t>
+  </si>
+  <si>
+    <t>Heathers No White.kst</t>
+  </si>
+  <si>
+    <t>Heathers.kst</t>
+  </si>
+  <si>
+    <t>Khaki No White.kst</t>
+  </si>
+  <si>
+    <t>Khaki W White.kst</t>
+  </si>
+  <si>
+    <t>Light 4C HQ V900.kst</t>
+  </si>
+  <si>
+    <t>Light 4C STD V900.kst</t>
+  </si>
+  <si>
+    <t>Light HP 4C EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Light HP 4C EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Light HP EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Light HP EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Light HQ 4C EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Light HQ 4C EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Light HQ EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Light HQ EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Light HQ V900.kst</t>
+  </si>
+  <si>
+    <t>Light No White.kst</t>
+  </si>
+  <si>
+    <t>Light STD 4C EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Light STD 4C EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Light STD EcoRapid_1.kst</t>
+  </si>
+  <si>
+    <t>Light STD EcoRapid.kst</t>
+  </si>
+  <si>
+    <t>Light STD V900.kst</t>
+  </si>
+  <si>
+    <t>Natural Heather.kst</t>
+  </si>
+  <si>
+    <t>Natural.kst</t>
+  </si>
+  <si>
+    <t>Navy Heather.kst</t>
+  </si>
+  <si>
+    <t>PAi Gildan 5000 Black.kst</t>
+  </si>
+  <si>
+    <t>PAi Gildan 5000 Red.kst</t>
+  </si>
+  <si>
+    <t>PAi Gildan 5000 White.kst</t>
+  </si>
+  <si>
+    <t>PAi Gildan 46000.kst</t>
+  </si>
+  <si>
+    <t>PAi Next Level.kst</t>
+  </si>
+  <si>
+    <t>Production Job.kst</t>
+  </si>
+  <si>
+    <t>Red Mist.kst</t>
+  </si>
+  <si>
+    <t>Royal Heather.kst</t>
+  </si>
+  <si>
+    <t>Royal Mist.kst</t>
+  </si>
+  <si>
+    <t>Smoke.kst</t>
+  </si>
+  <si>
+    <t>Test 2.kst</t>
+  </si>
+  <si>
+    <t>Test.kst</t>
+  </si>
+  <si>
+    <t>White Ink Only.kst</t>
+  </si>
+  <si>
+    <t>White.kst</t>
+  </si>
+  <si>
+    <t>VULCAN MEDIA</t>
+  </si>
+  <si>
+    <t>Dark STD C400x600D W600x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Dark STD C400x800D W600x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Dark STD C500x600D W600x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Dark STD C600x800 W600x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>linear45_1.lut</t>
+  </si>
+  <si>
+    <t>linear45_8x8.lut</t>
+  </si>
+  <si>
+    <t>linear45.lut</t>
+  </si>
+  <si>
+    <t>Machine9_DarkSTD.lut</t>
+  </si>
+  <si>
+    <t>Paper_BlackT600x600RG_1.lut</t>
+  </si>
+  <si>
+    <t>Paper_BlackT600x600RG.lut</t>
+  </si>
+  <si>
+    <t>Paper_WhiteT600x600RG_1.lut</t>
+  </si>
+  <si>
+    <t>Paper_WhiteT600x600RG.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HighestQ 4C 6x8D6x8 V900.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HighestQ 6x8D6x8 V900.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HP 4C W800x800 C500x600 EcoRapid_1.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HP 4C W800x800 C500x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HP 4C W1000x600C500x600.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HP W800x800 C500x600 EcoRapid_1.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HP W800x800 C500x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HP W1000x600C500x600.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HQ 4C W12x6 C6x8 V900.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HQ 4C W800x800 C800x600 EcoRapid_1.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HQ 4C W800x800 C800x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HQ W12x6 C6x8 V900.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HQ W800x800 C800x600 EcoRapid_1.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark HQ W800x800 C800x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark STD 4C W12x6 C6x6 V900.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark STD 4C W800x800 C600x600 EcoRapid_1.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark STD 4C W800x800 C600x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark STD W12x6 C6x6 V900.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark STD W600x800 C600x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark STD W800x800 C600x600 EcoRapid_1.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Dark STD W800x800 C600x600 EcoRapid.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HP 4C C500x600 EcoRapid_1.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HP 4C C500x600 EcoRapid.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HP C500x600 EcoRapid_1.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HP C500x600 EcoRapid.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HQ 4C 600X800 V900.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HQ 4C C800x800 EcoRapid_1.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HQ 4C C800x800 EcoRapid.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HQ 600X800 V900.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HQ C800x800 EcoRapid_1.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light HQ C800x800 EcoRapid.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light STD 4C 600X600 V900.Lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light STD 4C C600x600 EcoRapid_1.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light STD 4C C600x600 EcoRapid.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light STD 600X600 V900.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light STD C600x600 EcoRapid_1.lut</t>
+  </si>
+  <si>
+    <t>Vulcan Light STD C600x600 EcoRapid.lut</t>
+  </si>
+  <si>
+    <t>Input Profiles</t>
+  </si>
+  <si>
+    <t>Output Profiles</t>
+  </si>
+  <si>
+    <t>CoatedFOGRA39</t>
+  </si>
+  <si>
+    <t>EuroscaleCoated</t>
+  </si>
+  <si>
+    <t>Photoshop5DefaultCMYK</t>
+  </si>
+  <si>
+    <t>UncoatedFOGRA29</t>
+  </si>
+  <si>
+    <t>USWebCoatedSWOP</t>
+  </si>
+  <si>
+    <t>USWebUncoated</t>
+  </si>
+  <si>
+    <t>AdobeRGB1998</t>
+  </si>
+  <si>
+    <t>sRGB Color Space Profile</t>
+  </si>
+  <si>
+    <t>Chart 936 Patches</t>
+  </si>
+  <si>
+    <t>Vulcan Dark 4C EcoRapid</t>
+  </si>
+  <si>
+    <t>Vulcan Dark EcoRapid</t>
+  </si>
+  <si>
+    <t>Vulcan Dark RG</t>
+  </si>
+  <si>
+    <t>Vulcan Dark STD w6x8 c6x6 V105 v2</t>
+  </si>
+  <si>
+    <t>Vulcan Dark STD w6x8 c6x6 V105</t>
+  </si>
+  <si>
+    <t>Vulcan Dark V1</t>
+  </si>
+  <si>
+    <t>Vulcan Light 4C EcoRapid</t>
+  </si>
+  <si>
+    <t>Vulcan Light EcoRapid</t>
+  </si>
+  <si>
+    <t>Vulcan Light V1</t>
+  </si>
+  <si>
+    <t>Vulcan White RG</t>
+  </si>
+  <si>
+    <t>VULCAN SYSTEM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -131,16 +554,54 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -148,15 +609,210 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,115 +1147,832 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8ECBCF-6884-2D43-B923-2F4C6971AE05}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" customWidth="1"/>
+    <col min="2" max="2" width="47.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="47.5" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:9" ht="23" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="15"/>
+    </row>
+    <row r="2" spans="1:9" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="G4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="5"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="5"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="5"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="5"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="5"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="5"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="5"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="5"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="5"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="5"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="5"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="5"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="5"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="5"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="5"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="5"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="5"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="5"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="5"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="5"/>
+    </row>
+    <row r="74" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>